--- a/Questionnaires/IPQ_Block1.xlsx
+++ b/Questionnaires/IPQ_Block1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sowmya\QOE_CWI\RCQoEA_Github\RCQoEA-360VR-Dataset\Questionnaires\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BA7019-AA4B-4E35-A4B0-7D61258FDB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E42BB0-E61E-42DD-9306-EC98B50ECBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,13 +207,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -232,9 +232,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,69 +521,55 @@
     <col min="1" max="1" width="12.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-    </row>
-    <row r="2" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -873,130 +859,1222 @@
       <c r="A9" t="s">
         <v>3</v>
       </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>-3</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
+        <v>-3</v>
+      </c>
+      <c r="J9">
+        <v>-3</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="O9">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>4</v>
       </c>
+      <c r="B10">
+        <v>-2</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>-2</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>-3</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>-2</v>
+      </c>
+      <c r="O10">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>40</v>
       </c>
+      <c r="B11">
+        <v>-1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>-2</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>-2</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>-2</v>
+      </c>
+      <c r="M11">
+        <v>-3</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>5</v>
       </c>
+      <c r="B12">
+        <v>-3</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>-1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>-1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>-1</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>6</v>
       </c>
+      <c r="B13">
+        <v>-2</v>
+      </c>
+      <c r="C13">
+        <v>-2</v>
+      </c>
+      <c r="D13">
+        <v>-3</v>
+      </c>
+      <c r="E13">
+        <v>-1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>-1</v>
+      </c>
+      <c r="I13">
+        <v>-2</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>-2</v>
+      </c>
+      <c r="M13">
+        <v>-2</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>7</v>
       </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>-2</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>-2</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>41</v>
       </c>
+      <c r="B15">
+        <v>-1</v>
+      </c>
+      <c r="C15">
+        <v>-3</v>
+      </c>
+      <c r="D15">
+        <v>-1</v>
+      </c>
+      <c r="E15">
+        <v>-3</v>
+      </c>
+      <c r="F15">
+        <v>-2</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>-2</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15">
+        <v>-2</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>-2</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>-1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <v>3</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>2</v>
+      </c>
+      <c r="O18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B19">
+        <v>-2</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>-3</v>
+      </c>
+      <c r="I19">
+        <v>-3</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>-3</v>
+      </c>
+      <c r="M20">
+        <v>-1</v>
+      </c>
+      <c r="N20">
+        <v>-3</v>
+      </c>
+      <c r="O20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B21">
+        <v>-1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>-3</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>-2</v>
+      </c>
+      <c r="J21">
+        <v>3</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>-2</v>
+      </c>
+      <c r="M21">
+        <v>-3</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+      <c r="O21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>-1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>-1</v>
+      </c>
+      <c r="M22">
+        <v>-3</v>
+      </c>
+      <c r="N22">
+        <v>-2</v>
+      </c>
+      <c r="O22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>-1</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>-2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>-2</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>-1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24">
+        <v>2</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B25">
+        <v>-2</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>-1</v>
+      </c>
+      <c r="O25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>-3</v>
+      </c>
+      <c r="I26">
+        <v>-1</v>
+      </c>
+      <c r="J26">
+        <v>-3</v>
+      </c>
+      <c r="K26">
+        <v>-3</v>
+      </c>
+      <c r="L26">
+        <v>3</v>
+      </c>
+      <c r="M26">
+        <v>-3</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27">
+        <v>-1</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>-2</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>-1</v>
+      </c>
+      <c r="F29">
+        <v>-2</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>-1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>-1</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>-3</v>
+      </c>
+      <c r="N29">
+        <v>3</v>
+      </c>
+      <c r="O29">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>-2</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>-1</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>-2</v>
+      </c>
+      <c r="M30">
+        <v>-3</v>
+      </c>
+      <c r="N30">
+        <v>3</v>
+      </c>
+      <c r="O30">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>3</v>
+      </c>
+      <c r="H31">
+        <v>3</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31">
+        <v>3</v>
+      </c>
+      <c r="L31">
+        <v>-3</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>-2</v>
+      </c>
+      <c r="O31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+      <c r="H32">
+        <v>-1</v>
+      </c>
+      <c r="I32">
+        <v>-1</v>
+      </c>
+      <c r="J32">
+        <v>-1</v>
+      </c>
+      <c r="K32">
+        <v>-1</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>-1</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>-1</v>
+      </c>
+      <c r="E33">
+        <v>-2</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>-3</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>20</v>
+      </c>
+      <c r="B34">
+        <v>-3</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>3</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>3</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
